--- a/Dashboards/data/Data final/empleo/pobreza/pobreza_lab_educ.xlsx
+++ b/Dashboards/data/Data final/empleo/pobreza/pobreza_lab_educ.xlsx
@@ -101,10 +101,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>0.53055465221405029</v>
+        <v>0.59162509441375732</v>
       </c>
       <c r="D2" s="1">
-        <v>53.055465698242188</v>
+        <v>59.162509918212891</v>
       </c>
     </row>
     <row r="3">
@@ -115,10 +115,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>0.16122680902481079</v>
+        <v>0.18971717357635498</v>
       </c>
       <c r="D3" s="1">
-        <v>16.1226806640625</v>
+        <v>18.971717834472656</v>
       </c>
     </row>
     <row r="4">
@@ -129,10 +129,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>0.50414520502090454</v>
+        <v>0.5380290150642395</v>
       </c>
       <c r="D4" s="1">
-        <v>50.414520263671875</v>
+        <v>53.802902221679688</v>
       </c>
     </row>
     <row r="5">
@@ -143,10 +143,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>0.14467900991439819</v>
+        <v>0.14242410659790039</v>
       </c>
       <c r="D5" s="1">
-        <v>14.467901229858398</v>
+        <v>14.242410659790039</v>
       </c>
     </row>
     <row r="6">
@@ -157,10 +157,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>0.37797850370407104</v>
+        <v>0.4247492253780365</v>
       </c>
       <c r="D6" s="1">
-        <v>37.7978515625</v>
+        <v>42.474922180175781</v>
       </c>
     </row>
     <row r="7">
@@ -171,10 +171,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>0.057694502174854279</v>
+        <v>0.070219628512859344</v>
       </c>
       <c r="D7" s="1">
-        <v>5.7694501876831055</v>
+        <v>7.0219626426696777</v>
       </c>
     </row>
     <row r="8">
@@ -185,10 +185,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>0.31046432256698608</v>
+        <v>0.35051423311233521</v>
       </c>
       <c r="D8" s="1">
-        <v>31.046432495117188</v>
+        <v>35.051422119140625</v>
       </c>
     </row>
     <row r="9">
@@ -199,10 +199,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>0.041042298078536987</v>
+        <v>0.053430791944265366</v>
       </c>
       <c r="D9" s="1">
-        <v>4.1042299270629883</v>
+        <v>5.3430790901184082</v>
       </c>
     </row>
     <row r="10">
@@ -213,10 +213,10 @@
         <v>2</v>
       </c>
       <c r="C10" s="1">
-        <v>0.28629705309867859</v>
+        <v>0.32454466819763184</v>
       </c>
       <c r="D10" s="1">
-        <v>28.629705429077149</v>
+        <v>32.4544677734375</v>
       </c>
     </row>
     <row r="11">
@@ -227,10 +227,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="1">
-        <v>0.035544600337743759</v>
+        <v>0.039656482636928558</v>
       </c>
       <c r="D11" s="1">
-        <v>3.5544600486755371</v>
+        <v>3.9656481742858887</v>
       </c>
     </row>
     <row r="12">
@@ -241,10 +241,10 @@
         <v>2</v>
       </c>
       <c r="C12" s="1">
-        <v>0.28913906216621399</v>
+        <v>0.33415356278419495</v>
       </c>
       <c r="D12" s="1">
-        <v>28.913906097412109</v>
+        <v>33.415355682373047</v>
       </c>
     </row>
     <row r="13">
@@ -255,10 +255,10 @@
         <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>0.05185193195939064</v>
+        <v>0.069231346249580383</v>
       </c>
       <c r="D13" s="1">
-        <v>5.1851930618286133</v>
+        <v>6.9231348037719727</v>
       </c>
     </row>
     <row r="14">
@@ -269,10 +269,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="1">
-        <v>0.25697529315948486</v>
+        <v>0.30050387978553772</v>
       </c>
       <c r="D14" s="1">
-        <v>25.697528839111328</v>
+        <v>30.050388336181641</v>
       </c>
     </row>
     <row r="15">
@@ -283,10 +283,10 @@
         <v>3</v>
       </c>
       <c r="C15" s="1">
-        <v>0.039089322090148926</v>
+        <v>0.050398651510477066</v>
       </c>
       <c r="D15" s="1">
-        <v>3.9089322090148926</v>
+        <v>5.0398650169372559</v>
       </c>
     </row>
     <row r="16">
@@ -297,10 +297,10 @@
         <v>2</v>
       </c>
       <c r="C16" s="1">
-        <v>0.22521600127220154</v>
+        <v>0.25852802395820618</v>
       </c>
       <c r="D16" s="1">
-        <v>22.521600723266602</v>
+        <v>25.852802276611328</v>
       </c>
     </row>
     <row r="17">
@@ -311,10 +311,10 @@
         <v>3</v>
       </c>
       <c r="C17" s="1">
-        <v>0.028546309098601341</v>
+        <v>0.038904517889022827</v>
       </c>
       <c r="D17" s="1">
-        <v>2.8546309471130371</v>
+        <v>3.8904519081115723</v>
       </c>
     </row>
     <row r="18">
@@ -325,10 +325,10 @@
         <v>2</v>
       </c>
       <c r="C18" s="1">
-        <v>0.2063552737236023</v>
+        <v>0.24823082983493805</v>
       </c>
       <c r="D18" s="1">
-        <v>20.635526657104492</v>
+        <v>24.823083877563477</v>
       </c>
     </row>
     <row r="19">
@@ -339,10 +339,10 @@
         <v>3</v>
       </c>
       <c r="C19" s="1">
-        <v>0.027645761147141457</v>
+        <v>0.043935611844062805</v>
       </c>
       <c r="D19" s="1">
-        <v>2.7645761966705322</v>
+        <v>4.3935613632202149</v>
       </c>
     </row>
     <row r="20">
@@ -353,10 +353,10 @@
         <v>2</v>
       </c>
       <c r="C20" s="1">
-        <v>0.19324551522731781</v>
+        <v>0.22148498892784119</v>
       </c>
       <c r="D20" s="1">
-        <v>19.324550628662109</v>
+        <v>22.14849853515625</v>
       </c>
     </row>
     <row r="21">
@@ -367,10 +367,10 @@
         <v>3</v>
       </c>
       <c r="C21" s="1">
-        <v>0.018163062632083893</v>
+        <v>0.021847214549779892</v>
       </c>
       <c r="D21" s="1">
-        <v>1.8163062334060669</v>
+        <v>2.1847214698791504</v>
       </c>
     </row>
     <row r="22">
@@ -381,10 +381,10 @@
         <v>2</v>
       </c>
       <c r="C22" s="1">
-        <v>0.16434673964977264</v>
+        <v>0.19307838380336762</v>
       </c>
       <c r="D22" s="1">
-        <v>16.434673309326172</v>
+        <v>19.307838439941406</v>
       </c>
     </row>
     <row r="23">
@@ -395,10 +395,10 @@
         <v>3</v>
       </c>
       <c r="C23" s="1">
-        <v>0.020995570346713066</v>
+        <v>0.027471777051687241</v>
       </c>
       <c r="D23" s="1">
-        <v>2.0995569229125977</v>
+        <v>2.7471776008605957</v>
       </c>
     </row>
     <row r="24">
@@ -409,10 +409,10 @@
         <v>2</v>
       </c>
       <c r="C24" s="1">
-        <v>0.17009539902210236</v>
+        <v>0.20913504064083099</v>
       </c>
       <c r="D24" s="1">
-        <v>17.009540557861328</v>
+        <v>20.913503646850586</v>
       </c>
     </row>
     <row r="25">
@@ -423,10 +423,10 @@
         <v>3</v>
       </c>
       <c r="C25" s="1">
-        <v>0.022326635196805</v>
+        <v>0.031114773824810982</v>
       </c>
       <c r="D25" s="1">
-        <v>2.232663631439209</v>
+        <v>3.1114773750305176</v>
       </c>
     </row>
     <row r="26">
@@ -437,10 +437,10 @@
         <v>2</v>
       </c>
       <c r="C26" s="1">
-        <v>0.1737092137336731</v>
+        <v>0.21505816280841827</v>
       </c>
       <c r="D26" s="1">
-        <v>17.370922088623047</v>
+        <v>21.505815505981445</v>
       </c>
     </row>
     <row r="27">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="C27" s="1">
-        <v>0.022366547957062721</v>
+        <v>0.032083060592412949</v>
       </c>
       <c r="D27" s="1">
-        <v>2.2366547584533692</v>
+        <v>3.2083060741424561</v>
       </c>
     </row>
     <row r="28">
@@ -465,10 +465,10 @@
         <v>2</v>
       </c>
       <c r="C28" s="1">
-        <v>0.15764479339122772</v>
+        <v>0.20015157759189606</v>
       </c>
       <c r="D28" s="1">
-        <v>15.764479637145996</v>
+        <v>20.015157699584961</v>
       </c>
     </row>
     <row r="29">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="C29" s="1">
-        <v>0.021199390292167664</v>
+        <v>0.029818039387464523</v>
       </c>
       <c r="D29" s="1">
-        <v>2.1199390888214111</v>
+        <v>2.9818038940429688</v>
       </c>
     </row>
     <row r="30">
@@ -493,10 +493,10 @@
         <v>2</v>
       </c>
       <c r="C30" s="1">
-        <v>0.17044444382190704</v>
+        <v>0.25362393260002136</v>
       </c>
       <c r="D30" s="1">
-        <v>17.044445037841797</v>
+        <v>25.362392425537109</v>
       </c>
     </row>
     <row r="31">
@@ -507,10 +507,10 @@
         <v>3</v>
       </c>
       <c r="C31" s="1">
-        <v>0.017617223784327507</v>
+        <v>0.042130984365940094</v>
       </c>
       <c r="D31" s="1">
-        <v>1.7617223262786865</v>
+        <v>4.2130985260009766</v>
       </c>
     </row>
     <row r="32">
@@ -521,10 +521,10 @@
         <v>2</v>
       </c>
       <c r="C32" s="1">
-        <v>0.18272727727890015</v>
+        <v>0.23481085896492004</v>
       </c>
       <c r="D32" s="1">
-        <v>18.272727966308594</v>
+        <v>23.481086730957031</v>
       </c>
     </row>
     <row r="33">
@@ -535,10 +535,10 @@
         <v>3</v>
       </c>
       <c r="C33" s="1">
-        <v>0.023570286110043526</v>
+        <v>0.034815080463886261</v>
       </c>
       <c r="D33" s="1">
-        <v>2.3570287227630615</v>
+        <v>3.4815080165863037</v>
       </c>
     </row>
     <row r="34">
@@ -549,10 +549,10 @@
         <v>2</v>
       </c>
       <c r="C34" s="1">
-        <v>0.24577270448207855</v>
+        <v>0.30311787128448486</v>
       </c>
       <c r="D34" s="1">
-        <v>24.5772705078125</v>
+        <v>30.311786651611328</v>
       </c>
     </row>
     <row r="35">
@@ -563,10 +563,10 @@
         <v>3</v>
       </c>
       <c r="C35" s="1">
-        <v>0.045294038951396942</v>
+        <v>0.061338014900684357</v>
       </c>
       <c r="D35" s="1">
-        <v>4.5294036865234375</v>
+        <v>6.1338014602661133</v>
       </c>
     </row>
     <row r="36">
@@ -577,10 +577,10 @@
         <v>2</v>
       </c>
       <c r="C36" s="1">
-        <v>0.2217617928981781</v>
+        <v>0.2643018364906311</v>
       </c>
       <c r="D36" s="1">
-        <v>22.176179885864258</v>
+        <v>26.430183410644531</v>
       </c>
     </row>
     <row r="37">
@@ -591,10 +591,10 @@
         <v>3</v>
       </c>
       <c r="C37" s="1">
-        <v>0.054529339075088501</v>
+        <v>0.036435317248106003</v>
       </c>
       <c r="D37" s="1">
-        <v>5.4529337882995605</v>
+        <v>3.6435317993164063</v>
       </c>
     </row>
     <row r="38">
@@ -605,10 +605,10 @@
         <v>2</v>
       </c>
       <c r="C38" s="1">
-        <v>0.19155827164649963</v>
+        <v>0.23503361642360687</v>
       </c>
       <c r="D38" s="1">
-        <v>19.155826568603516</v>
+        <v>23.503360748291016</v>
       </c>
     </row>
     <row r="39">
@@ -619,10 +619,10 @@
         <v>3</v>
       </c>
       <c r="C39" s="1">
-        <v>0.024487771093845367</v>
+        <v>0.017605116590857506</v>
       </c>
       <c r="D39" s="1">
-        <v>2.4487771987915039</v>
+        <v>1.7605116367340088</v>
       </c>
     </row>
     <row r="40">
@@ -633,10 +633,10 @@
         <v>2</v>
       </c>
       <c r="C40" s="1">
-        <v>0.19374783337116241</v>
+        <v>0.23283722996711731</v>
       </c>
       <c r="D40" s="1">
-        <v>19.374782562255859</v>
+        <v>23.283723831176758</v>
       </c>
     </row>
     <row r="41">
@@ -647,10 +647,10 @@
         <v>3</v>
       </c>
       <c r="C41" s="1">
-        <v>0.022807810455560684</v>
+        <v>0.028170958161354065</v>
       </c>
       <c r="D41" s="1">
-        <v>2.2807810306549072</v>
+        <v>2.8170957565307617</v>
       </c>
     </row>
     <row r="42">
@@ -661,10 +661,10 @@
         <v>2</v>
       </c>
       <c r="C42" s="1">
-        <v>0.20053219795227051</v>
+        <v>0.24156066775321961</v>
       </c>
       <c r="D42" s="1">
-        <v>20.053218841552734</v>
+        <v>24.15606689453125</v>
       </c>
     </row>
     <row r="43">
@@ -675,10 +675,10 @@
         <v>3</v>
       </c>
       <c r="C43" s="1">
-        <v>0.028452064841985703</v>
+        <v>0.033687453716993332</v>
       </c>
       <c r="D43" s="1">
-        <v>2.8452064990997315</v>
+        <v>3.3687453269958496</v>
       </c>
     </row>
     <row r="44">
@@ -689,10 +689,10 @@
         <v>2</v>
       </c>
       <c r="C44" s="1">
-        <v>0.17204608023166656</v>
+        <v>0.19780787825584412</v>
       </c>
       <c r="D44" s="1">
-        <v>17.204608917236328</v>
+        <v>19.780788421630859</v>
       </c>
     </row>
     <row r="45">
@@ -703,10 +703,10 @@
         <v>3</v>
       </c>
       <c r="C45" s="1">
-        <v>0.013631212525069714</v>
+        <v>0.022341703996062279</v>
       </c>
       <c r="D45" s="1">
-        <v>1.3631212711334229</v>
+        <v>2.2341704368591309</v>
       </c>
     </row>
   </sheetData>
